--- a/Dados/Brutos/pib_munic.xlsx
+++ b/Dados/Brutos/pib_munic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Documents\Projetos Python\proj_munic_sc\Dados\Brutos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Desktop\proj_munic_sc\Dados\Brutos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6737A4FF-543A-446B-92ED-3698AB97F4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBEA523-5CE5-456C-8C99-6BF825ED84F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{427D240D-606B-439F-AE1F-F6EB6D385DA6}"/>
   </bookViews>
@@ -1304,7 +1304,9 @@
   <dimension ref="A1:W296"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="21" width="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -10463,7 +10465,7 @@
         <v>55675172013.511688</v>
       </c>
       <c r="W129">
-        <v>48195909000</v>
+        <v>60107728964.780403</v>
       </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
@@ -10676,7 +10678,7 @@
         <v>2165750524.2748036</v>
       </c>
       <c r="W132">
-        <v>1990651000</v>
+        <v>2361126094.896348</v>
       </c>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
@@ -18699,7 +18701,7 @@
         <v>8470018440.2322674</v>
       </c>
       <c r="W245">
-        <v>7396332000</v>
+        <v>8908625235.5323544</v>
       </c>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
